--- a/05_Figures/F06_prediction/proteins/T1/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_fcsa_II/spls/c_data/results.xlsx
@@ -143,264 +143,264 @@
     <t xml:space="preserve">HDHD2</t>
   </si>
   <si>
+    <t xml:space="preserve">METAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMTOR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAB1A</t>
   </si>
   <si>
-    <t xml:space="preserve">METAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR3</t>
+    <t xml:space="preserve">ZYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFAP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHD</t>
   </si>
   <si>
     <t xml:space="preserve">SRSF2</t>
   </si>
   <si>
-    <t xml:space="preserve">ZYX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFAP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHD</t>
-  </si>
-  <si>
     <t xml:space="preserve">UQCRH</t>
   </si>
   <si>
-    <t xml:space="preserve">MAP2K2</t>
+    <t xml:space="preserve">EEA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPO</t>
   </si>
   <si>
     <t xml:space="preserve">ALDH5A1</t>
   </si>
   <si>
+    <t xml:space="preserve">ARMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOML2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1E</t>
+  </si>
+  <si>
     <t xml:space="preserve">COPS7A</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF3G</t>
+    <t xml:space="preserve">FUNDC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPPL2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UROD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDR61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORASP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADHB</t>
   </si>
   <si>
     <t xml:space="preserve">HSD17B4</t>
   </si>
   <si>
-    <t xml:space="preserve">SPPL2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STOML2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUM</t>
+    <t xml:space="preserve">MT-ND1</t>
   </si>
   <si>
     <t xml:space="preserve">MYH14</t>
   </si>
   <si>
+    <t xml:space="preserve">PSMB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAND1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRSF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAF5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTC</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLC16A1</t>
   </si>
   <si>
-    <t xml:space="preserve">SNTB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDR61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAF5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFPQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMM22</t>
+    <t xml:space="preserve">TXNRD1</t>
   </si>
   <si>
     <t xml:space="preserve">AHCYL2</t>
   </si>
   <si>
-    <t xml:space="preserve">CAND1</t>
+    <t xml:space="preserve">BSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMTNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNDC17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADPRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR7A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANP32A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2</t>
   </si>
   <si>
     <t xml:space="preserve">CHMP2A</t>
   </si>
   <si>
+    <t xml:space="preserve">COPS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX6</t>
+  </si>
+  <si>
     <t xml:space="preserve">ELOB</t>
   </si>
   <si>
-    <t xml:space="preserve">GAMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MT-ND1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMTNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXNDC17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXNRD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADPRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR7A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANP32A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ8A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEA1</t>
-  </si>
-  <si>
     <t xml:space="preserve">EPB41L2</t>
   </si>
   <si>
+    <t xml:space="preserve">EPM2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAPDHS</t>
+  </si>
+  <si>
     <t xml:space="preserve">GFM1</t>
   </si>
   <si>
-    <t xml:space="preserve">GORASP2</t>
+    <t xml:space="preserve">GGCT</t>
   </si>
   <si>
     <t xml:space="preserve">GPS1</t>
   </si>
   <si>
-    <t xml:space="preserve">GRSF1</t>
-  </si>
-  <si>
     <t xml:space="preserve">H1-5</t>
   </si>
   <si>
-    <t xml:space="preserve">IQGAP1</t>
-  </si>
-  <si>
     <t xml:space="preserve">KARS1</t>
   </si>
   <si>
-    <t xml:space="preserve">MME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTF1</t>
+    <t xml:space="preserve">NDRG2</t>
   </si>
   <si>
     <t xml:space="preserve">PDP1</t>
   </si>
   <si>
-    <t xml:space="preserve">PDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2CA</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRKAA2</t>
   </si>
   <si>
+    <t xml:space="preserve">PRUNE1</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMA3</t>
   </si>
   <si>
@@ -416,12 +416,6 @@
     <t xml:space="preserve">RUVBL2</t>
   </si>
   <si>
-    <t xml:space="preserve">SCN1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A13</t>
-  </si>
-  <si>
     <t xml:space="preserve">SNRPD3</t>
   </si>
   <si>
@@ -431,6 +425,15 @@
     <t xml:space="preserve">SNX5</t>
   </si>
   <si>
+    <t xml:space="preserve">SPCS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STT3A</t>
+  </si>
+  <si>
     <t xml:space="preserve">STX7</t>
   </si>
   <si>
@@ -441,9 +444,6 @@
   </si>
   <si>
     <t xml:space="preserve">TUBB4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UROD</t>
   </si>
   <si>
     <t xml:space="preserve">ZBTB9</t>
@@ -833,13 +833,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.329385394890014</v>
+        <v>-0.253512051056324</v>
       </c>
       <c r="I2" t="n">
         <v>0.164285714285714</v>
@@ -866,29 +866,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.329385394890014</v>
+        <v>-0.253512051056324</v>
       </c>
       <c r="I3" t="n">
         <v>0.164285714285714</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.223880597014925</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.624575277148864</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.703446200025977</v>
-      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -912,2206 +904,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.617540929357618</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.0194005494831799</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.00956476474673329</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.938137879762347</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.168373257975682</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.907583437239881</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.157894787373924</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.299993297970991</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.83762455871356</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.629196799210153</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.577503471940321</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.80504833732933</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.749450734460734</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.547383324828458</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.134472415911894</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.295114066723216</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.47996316542093</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-1.75382548139311</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.17914678237022</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.78894618790576</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.819393325835052</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.121942919020827</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.99959575049211</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.950827329563585</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.352894029783033</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.79370957935478</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.596821415971948</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.00833299810934995</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.481050599535495</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.812889599950754</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.0829768492433208</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.21867127023365</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.142332011333816</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.853005661697986</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-1.14873469077936</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.55679914235814</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.853395792813095</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.824152809922117</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.659130136042271</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.791050895922299</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.358770918117201</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.951163544590624</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.806310912804062</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.33437361422481</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.626943763808854</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-2.05577759668781</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.191498968973769</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.397911970144061</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0135166088439966</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.649092725237651</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.423407413654052</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.513543507016474</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.444357528922318</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.678006839339925</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.402294697099617</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.1769367405465</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.13230800898681</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.65765653945602</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.00597928574125317</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.864184366571127</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.948227605284359</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.0549406498825943</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.805760507928099</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.299934432928021</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.492006714378754</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.581192953613679</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.405332369894059</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.621573073655546</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.10018900048196</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.904608930942754</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.00251119325628146</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.51573467018089</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.20745686142381</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-1.00296459814716</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.408154996237373</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.910615134044453</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.305523838050897</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.697028604126463</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.11649221690722</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.102527645281604</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.727017579454266</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-1.25200386578469</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.509141450308457</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.961248340142619</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0.139366467968371</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.0366660378712477</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.66762093032866</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.175696631453556</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.224068542680926</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.276197390705784</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.507315850333478</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0.0642233810337348</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.338708867413463</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.37905139096462</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.31937272188359</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.35218469677474</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.373302383659307</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.0773422814512152</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.217868806280717</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.06385836062883</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.34371526718238</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-1.5020671842507</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.057673909363</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.122958727632995</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.606712552290161</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.988644562211243</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.451169817016879</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.250647461532819</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.2003267998994</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.152860363825448</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.375221612995579</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.251442316566894</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.22665605668853</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.859119652462002</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.0330052184864471</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-6.36826850158716</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-1.54115136350032</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.68116426599794</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.134657539497727</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.11031000119753</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.893240290617941</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.68576247183396</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>0.326978661714775</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.353902134878819</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.89241565525875</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.89443799246647</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0.072429142841782</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.504633699917819</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.17018073425551</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.69397551296856</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.330712123369506</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-1.03087244949595</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.7563088832427</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0.313523368836555</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.260748555585038</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.374840875348675</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.21619250296503</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.58260752496108</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-1.28967993182579</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.730158469368553</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.429863246287414</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.750660335920341</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0.0591919098747087</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.440464629545911</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.808022804666006</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.660092467165949</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.36301912528129</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.283495207675791</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-1.34491387152313</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.589421050880269</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0.411474614736916</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.867008368797191</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.445612241052984</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.869594739572741</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>0.170487749486596</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.578672000406939</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.12584955472616</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>0.371800896346898</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.237701517661933</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.523254646851721</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.177724311401053</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.0130544755060293</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.327004705007296</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.902140801890654</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.659154229466309</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.848488864766</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.246396532937878</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.600984505563895</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.902918187219646</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.09146834920293</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.55462532454628</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.777524361475843</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.234277080973936</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.153301289021955</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.21179072764609</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-1.43781285632342</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.32327121473723</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.65962617999946</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.310983810172325</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.174809576247597</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.334106736197416</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.923443473846996</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0.265276160911081</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.65476999791055</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.668575396002293</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.14015635017853</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.27982152327352</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.601804028552587</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-2.2879648171047</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.126944068338183</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.227711557528252</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.783428562986143</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.893501770461631</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.312143599084866</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.64823540950659</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>0.399037765971799</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>0.261751741475706</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.14922888152896</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.415235225288151</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.869288410627457</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3154,7 +946,7 @@
         <v>517.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-663.071772799641</v>
+        <v>-649.951550425434</v>
       </c>
     </row>
     <row r="3">
@@ -3171,7 +963,7 @@
         <v>1517.85</v>
       </c>
       <c r="E3" t="n">
-        <v>361.404783299485</v>
+        <v>263.248000691089</v>
       </c>
     </row>
     <row r="4">
@@ -3188,7 +980,7 @@
         <v>2790.83</v>
       </c>
       <c r="E4" t="n">
-        <v>477.406706495011</v>
+        <v>518.610239651474</v>
       </c>
     </row>
     <row r="5">
@@ -3205,7 +997,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-147.653076955163</v>
+        <v>4.81754263832609</v>
       </c>
     </row>
     <row r="6">
@@ -3222,7 +1014,7 @@
         <v>1179</v>
       </c>
       <c r="E6" t="n">
-        <v>585.508591428519</v>
+        <v>405.795164872611</v>
       </c>
     </row>
     <row r="7">
@@ -3239,7 +1031,7 @@
         <v>682.55</v>
       </c>
       <c r="E7" t="n">
-        <v>-642.496620482756</v>
+        <v>-696.513113388683</v>
       </c>
     </row>
     <row r="8">
@@ -3256,7 +1048,7 @@
         <v>882.37</v>
       </c>
       <c r="E8" t="n">
-        <v>-84.6539654662252</v>
+        <v>35.3292646783411</v>
       </c>
     </row>
     <row r="9">
@@ -3273,7 +1065,7 @@
         <v>-171.76</v>
       </c>
       <c r="E9" t="n">
-        <v>184.639514050128</v>
+        <v>179.346645344686</v>
       </c>
     </row>
     <row r="10">
@@ -3290,7 +1082,7 @@
         <v>854.04</v>
       </c>
       <c r="E10" t="n">
-        <v>802.17516374424</v>
+        <v>699.539673627921</v>
       </c>
     </row>
     <row r="11">
@@ -3307,7 +1099,7 @@
         <v>-1503.6</v>
       </c>
       <c r="E11" t="n">
-        <v>1033.50816583807</v>
+        <v>1014.1346032646</v>
       </c>
     </row>
     <row r="12">
@@ -3324,7 +1116,7 @@
         <v>-88.7199999999993</v>
       </c>
       <c r="E12" t="n">
-        <v>-695.883324891691</v>
+        <v>-422.527753629265</v>
       </c>
     </row>
     <row r="13">
@@ -3341,7 +1133,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E13" t="n">
-        <v>243.320262764925</v>
+        <v>237.275269927065</v>
       </c>
     </row>
     <row r="14">
@@ -3358,7 +1150,7 @@
         <v>-1179.58</v>
       </c>
       <c r="E14" t="n">
-        <v>-2007.97640575439</v>
+        <v>-1253.93789670205</v>
       </c>
     </row>
     <row r="15">
@@ -3375,7 +1167,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E15" t="n">
-        <v>557.970578445214</v>
+        <v>498.837059981318</v>
       </c>
     </row>
     <row r="16">
@@ -3392,7 +1184,7 @@
         <v>-1081</v>
       </c>
       <c r="E16" t="n">
-        <v>-3330.92956497821</v>
+        <v>-3176.79484464157</v>
       </c>
     </row>
   </sheetData>
@@ -3553,10 +1345,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3570,10 +1362,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3587,10 +1379,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3604,10 +1396,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3621,10 +1413,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3638,10 +1430,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3672,10 +1464,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -3689,10 +1481,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
@@ -3706,10 +1498,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0.466666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
@@ -3723,10 +1515,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3740,10 +1532,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -3757,10 +1549,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -3774,10 +1566,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
@@ -3791,10 +1583,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -3808,10 +1600,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -3825,10 +1617,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.266666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -3842,10 +1634,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.266666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
@@ -3859,10 +1651,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -3876,10 +1668,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -3893,10 +1685,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -3910,10 +1702,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -3927,10 +1719,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -3944,10 +1736,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -3961,10 +1753,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -3978,10 +1770,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -3995,10 +1787,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="36">
@@ -4012,10 +1804,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="37">
@@ -4029,10 +1821,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -4046,10 +1838,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="39">
@@ -4063,10 +1855,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -4080,10 +1872,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -4097,10 +1889,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>0.133333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -4114,10 +1906,10 @@
         <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
@@ -4131,10 +1923,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -4148,10 +1940,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -4165,10 +1957,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
@@ -4182,10 +1974,10 @@
         <v>82</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="47">
@@ -4199,10 +1991,10 @@
         <v>83</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -4216,10 +2008,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
@@ -4233,10 +2025,10 @@
         <v>85</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="50">
@@ -4369,10 +2161,10 @@
         <v>93</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -4386,10 +2178,10 @@
         <v>94</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="59">

--- a/05_Figures/F06_prediction/proteins/T1/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_fcsa_II/spls/c_data/results.xlsx
@@ -869,7 +869,7 @@
         <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.253512051056324</v>
@@ -877,10 +877,18 @@
       <c r="I3" t="n">
         <v>0.164285714285714</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.263681592039801</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.248756218905473</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.644944099764697</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.795772969836173</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -904,6 +912,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.843659284743888</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0802044469915183</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0753605334454267</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.13281252274017</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0517163103796012</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.916001383502816</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.0813467462318793</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.322448713338399</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.04196606531472</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.479780256952041</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.659798507313297</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.667917883822656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.731116926752591</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.575717442355266</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.167506488480268</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.302546830178557</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.11877886139057</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.61204294456473</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.257352560112891</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.797640020836287</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.646006532257805</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.687720178018985</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.86357380510362</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.98584626893371</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.336734382762802</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.82804282233157</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.605010749862645</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.239241071501076</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.492042120281128</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.817707042184349</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0738405977058622</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.38436179369457</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.229019731679768</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.557044416786376</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.22505529009464</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.605286605720779</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.937434460644012</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.07854532723308</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.666537038311833</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.742023065170479</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.409329882555188</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.991261186761842</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.90283131307606</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.366616218357691</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.621658287118192</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-2.20217247045608</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.187518002493387</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.406811642214888</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.0734022721695142</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.549126950470759</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.392199794867855</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.463288773607797</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.401033345198838</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.70760491518233</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.363631916773948</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.02190741123438</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-8.25172833654903</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.50679194628923</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.406728168135349</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.18950816001354</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.00704464918566</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.0465621514622343</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.853868112254082</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.247108524433103</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.325253571307693</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.583466404650024</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.36556745677818</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.638925662653637</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.02232135072919</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.945214071023087</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.0650731071419741</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.724314050388639</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.0550854851965</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.995050355964674</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.340135363232914</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.801651675527417</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.399387687654022</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.662685015720493</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.35930264444604</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.120578110811128</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.773729250090073</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-1.33046416765905</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.542426339539141</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.795993119579189</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.196840345697623</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.101644828338744</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.63585873937136</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.176699242768108</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.226899913567321</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.465213066982984</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.480656193788367</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.042835386380615</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.279327905435013</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.37506177573957</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.290883297674703</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.72188041664845</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.509555065383937</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.0167294498067234</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.254115800020109</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.07423467388942</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.25793352009889</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-1.45203454168491</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.21600559633936</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.0537253346577353</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.825996020016685</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.94754840482294</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.264408761203649</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.504756734952264</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.308825325331955</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.23361339743374</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.279161112566597</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.201789489868548</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.18866750525616</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.751390092174064</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.681627273945116</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.22078060135706</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1.92097226388251</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.77600178016762</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.26884376496316</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.88097993515873</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.945896810152733</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.487758874853615</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.303861598951304</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.324731679626117</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.66776242641154</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.553966645460772</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.344075786530658</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.635593175235099</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.27485225410386</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.639935181935306</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.680071972769731</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.996850883532302</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.721154497620282</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.306018233141648</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.253718411726907</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.377822300687368</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.17603950197736</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.65191756401804</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-1.19562139800764</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.58842473884647</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.379117403607893</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.780777565680461</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.00529255373811721</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.470876020596491</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.03355412616169</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.261309493201134</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.48907148812177</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.46366219048399</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.15723751404507</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.415380970014359</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.392696446758971</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.14888954227707</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.65880497665423</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.69501315619161</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.164387545176963</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.651465633733817</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.117970285427787</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.615084856576581</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.235366339720196</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.74244370901864</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.144002472255761</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.0538401874602603</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.683896662109931</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.876906026610662</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.588468849663647</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.49776392717659</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.171523499561263</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.643686328267314</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.577116922309026</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.979694894443279</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.93611393754725</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.513241745521217</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.131720243642868</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.105047635500166</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.20315707760723</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-2.13096613061424</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.52644240830981</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.653236536100985</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.28240615403284</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.341309254217758</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.46108412880803</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.547042916164034</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.2156905916743</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.56054143665843</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.650824809346345</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.62607344719351</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.26456842327904</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.6695084795143</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.16899156710287</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.0629977408254094</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.223427482864498</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.789987893912323</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.830802877639153</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.340901896322644</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.85007824012442</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.33939882093856</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.312421413884039</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.11024892704957</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.532724932651285</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.870334486953099</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
